--- a/exports/COALINDIA_full_report.xlsx
+++ b/exports/COALINDIA_full_report.xlsx
@@ -4697,7 +4697,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>414.5376044076245</v>
+        <v>411.7879416239923</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -6740,16 +6740,16 @@
         <v>390.65</v>
       </c>
       <c r="E59" t="n">
-        <v>400.6</v>
+        <v>393.25</v>
       </c>
       <c r="F59" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G59" t="n">
         <v>9.56</v>
       </c>
       <c r="H59" t="n">
-        <v>-4.89</v>
+        <v>-6.64</v>
       </c>
       <c r="I59" t="n">
         <v>2.3</v>

--- a/exports/COALINDIA_full_report.xlsx
+++ b/exports/COALINDIA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.49</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>147.95</v>
+        <v>145.7</v>
       </c>
       <c r="I2" t="n">
         <v>146.6777024974715</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4</v>
+        <v>-1.92</v>
       </c>
       <c r="L2" t="n">
-        <v>1.58</v>
+        <v>2.36</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>7.27</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44600.55208333334</v>
+        <v>44601.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>148.65</v>
+        <v>155.2</v>
       </c>
       <c r="I3" t="n">
         <v>153.8131728950715</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.02</v>
+        <v>-6.52</v>
       </c>
       <c r="L3" t="n">
-        <v>5.42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M3" t="n">
         <v>1.55</v>
       </c>
       <c r="N3" t="n">
-        <v>2.85</v>
+        <v>5.82</v>
       </c>
       <c r="O3" t="n">
         <v>-1.49</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.27</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.55208333334</v>
+        <v>44614.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>150</v>
+        <v>147.25</v>
       </c>
       <c r="I4" t="n">
         <v>147.6007022364215</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.35</v>
+        <v>-5.12</v>
       </c>
       <c r="L4" t="n">
-        <v>4.12</v>
+        <v>6.7</v>
       </c>
       <c r="M4" t="n">
         <v>2.47</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>6.16</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44617.38541666666</v>
+        <v>44617.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>148.25</v>
+        <v>152.05</v>
       </c>
       <c r="I5" t="n">
         <v>151.4440771004969</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.68</v>
+        <v>-3.26</v>
       </c>
       <c r="L5" t="n">
-        <v>2.61</v>
+        <v>4.24</v>
       </c>
       <c r="M5" t="n">
         <v>0.78</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.26</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44634.55208333334</v>
+        <v>44635.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>167.35</v>
+        <v>161</v>
       </c>
       <c r="I6" t="n">
         <v>161.5035736619714</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>10.06</v>
+        <v>5.89</v>
       </c>
       <c r="L6" t="n">
         <v>3.06</v>
@@ -783,7 +854,7 @@
         <v>1.5</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="O6" t="n">
         <v>8.140000000000001</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>10.76</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44644.38541666666</v>
+        <v>44644.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>173.75</v>
+        <v>174.15</v>
       </c>
       <c r="I7" t="n">
         <v>174.1212009186771</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.92</v>
+        <v>-8.17</v>
       </c>
       <c r="L7" t="n">
-        <v>8.880000000000001</v>
+        <v>9.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.55</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.39</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44676.38541666666</v>
+        <v>44676.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>178.75</v>
+        <v>176.1</v>
       </c>
       <c r="I8" t="n">
         <v>177.0269574623895</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K8" t="n">
-        <v>2.64</v>
+        <v>1.12</v>
       </c>
       <c r="L8" t="n">
         <v>2.9</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44697.55208333334</v>
+        <v>44698.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>160.35</v>
+        <v>170.55</v>
       </c>
       <c r="I9" t="n">
         <v>170.4545125591852</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>8.94</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
         <v>2.04</v>
@@ -954,7 +1061,7 @@
         <v>1.59</v>
       </c>
       <c r="N9" t="n">
-        <v>2.56</v>
+        <v>7.3</v>
       </c>
       <c r="O9" t="n">
         <v>-6.73</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>11.98</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44727.55208333334</v>
+        <v>44728.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>177.1</v>
+        <v>170.8</v>
       </c>
       <c r="I10" t="n">
         <v>175.0169998402665</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>3.84</v>
+        <v>0.15</v>
       </c>
       <c r="L10" t="n">
         <v>5.48</v>
@@ -1011,7 +1130,7 @@
         <v>2.29</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>5.51</v>
       </c>
       <c r="O10" t="n">
         <v>7.3</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>9.18</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44741.38541666666</v>
+        <v>44741.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>174.6</v>
+        <v>175.4</v>
       </c>
       <c r="I11" t="n">
         <v>175.2272773148248</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.22</v>
+        <v>-2.69</v>
       </c>
       <c r="L11" t="n">
         <v>5.09</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.7</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44825.55208333334</v>
+        <v>44826.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>215.25</v>
+        <v>212.05</v>
       </c>
       <c r="I12" t="n">
         <v>212.1104486052857</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>84</v>
+        <v>84.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>22.72</v>
+        <v>20.9</v>
       </c>
       <c r="L12" t="n">
         <v>6.16</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>5.05</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>208.3</v>
+        <v>216</v>
       </c>
       <c r="I13" t="n">
         <v>208.5221498880654</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>1.77</v>
+        <v>-1.86</v>
       </c>
       <c r="L13" t="n">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
         <v>1.62</v>
       </c>
       <c r="N13" t="n">
-        <v>4.15</v>
+        <v>4.49</v>
       </c>
       <c r="O13" t="n">
         <v>-1.58</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.99</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44879.55208333334</v>
+        <v>44880.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>229.8</v>
+        <v>215.65</v>
       </c>
       <c r="I14" t="n">
         <v>229.0128579859008</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K14" t="n">
-        <v>6.39</v>
+        <v>-0.16</v>
       </c>
       <c r="L14" t="n">
         <v>3.24</v>
       </c>
       <c r="M14" t="n">
-        <v>1.81</v>
+        <v>5.05</v>
       </c>
       <c r="N14" t="n">
-        <v>2.61</v>
+        <v>5.81</v>
       </c>
       <c r="O14" t="n">
         <v>4.49</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>8.85</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>209.5</v>
+        <v>210.3</v>
       </c>
       <c r="I15" t="n">
         <v>209.7018667662144</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K15" t="n">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="L15" t="n">
         <v>3.11</v>
       </c>
       <c r="M15" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="N15" t="n">
         <v>2.46</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>3.67</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44929.55208333334</v>
+        <v>44930.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>208.65</v>
+        <v>202.4</v>
       </c>
       <c r="I16" t="n">
         <v>202.5847055856725</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.78</v>
+        <v>-3.76</v>
       </c>
       <c r="L16" t="n">
-        <v>1.28</v>
+        <v>4.26</v>
       </c>
       <c r="M16" t="n">
         <v>-0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.36</v>
+        <v>3.21</v>
       </c>
       <c r="O16" t="n">
         <v>-0.05</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>5.61</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44945.38541666666</v>
+        <v>44945.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>204.9</v>
+        <v>208.6</v>
       </c>
       <c r="I17" t="n">
         <v>205.3962678756849</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.24</v>
+        <v>-3.06</v>
       </c>
       <c r="L17" t="n">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.16</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.99</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44958.55208333334</v>
+        <v>44959.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>205.75</v>
+        <v>203.7</v>
       </c>
       <c r="I18" t="n">
         <v>205.2318240387021</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.37</v>
+        <v>-2.35</v>
       </c>
       <c r="L18" t="n">
         <v>4.34</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>6.3</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44986.55208333334</v>
+        <v>44987.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>203.7</v>
+        <v>208.05</v>
       </c>
       <c r="I19" t="n">
         <v>204.8041813905846</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-2.14</v>
       </c>
       <c r="L19" t="n">
-        <v>1.23</v>
+        <v>2.55</v>
       </c>
       <c r="M19" t="n">
         <v>0.46</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>5.38</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45002.55208333334</v>
+        <v>45005.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>205.75</v>
+        <v>201.6</v>
       </c>
       <c r="I20" t="n">
         <v>201.8584691096155</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.11</v>
+        <v>-3.1</v>
       </c>
       <c r="L20" t="n">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
       <c r="M20" t="n">
         <v>0.86</v>
       </c>
       <c r="N20" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
         <v>1.87</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.9</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>198.5</v>
+        <v>203.75</v>
       </c>
       <c r="I21" t="n">
         <v>201.7981794880324</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>1.54</v>
+        <v>-1.07</v>
       </c>
       <c r="L21" t="n">
         <v>2.28</v>
@@ -1638,7 +1889,7 @@
         <v>0.52</v>
       </c>
       <c r="N21" t="n">
-        <v>1.28</v>
+        <v>3.32</v>
       </c>
       <c r="O21" t="n">
         <v>-1.8</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>5.24</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45077.55208333334</v>
+        <v>45078.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>224.8</v>
+        <v>213.95</v>
       </c>
       <c r="I22" t="n">
         <v>221.4191588275236</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K22" t="n">
-        <v>10.33</v>
+        <v>5.01</v>
       </c>
       <c r="L22" t="n">
         <v>2.33</v>
       </c>
       <c r="M22" t="n">
-        <v>2.15</v>
+        <v>4.58</v>
       </c>
       <c r="N22" t="n">
-        <v>1.92</v>
+        <v>4.76</v>
       </c>
       <c r="O22" t="n">
         <v>3.32</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>5.76</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>211.8</v>
+        <v>213.65</v>
       </c>
       <c r="I23" t="n">
         <v>213.4124511630721</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0.14</v>
       </c>
       <c r="L23" t="n">
         <v>1.54</v>
@@ -1752,7 +2027,7 @@
         <v>0.91</v>
       </c>
       <c r="N23" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="O23" t="n">
         <v>-4.76</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>3.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45124.55208333334</v>
+        <v>45125.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>214.5</v>
+        <v>213.05</v>
       </c>
       <c r="I24" t="n">
         <v>213.2704623385154</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4</v>
+        <v>-0.28</v>
       </c>
       <c r="L24" t="n">
         <v>1.19</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>3.93</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45138.55208333334</v>
+        <v>45139.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>213.5</v>
+        <v>223.55</v>
       </c>
       <c r="I25" t="n">
         <v>218.0087031055544</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.21</v>
+        <v>-4.93</v>
       </c>
       <c r="L25" t="n">
-        <v>1.57</v>
+        <v>5.09</v>
       </c>
       <c r="M25" t="n">
         <v>0.53</v>
       </c>
       <c r="N25" t="n">
-        <v>0.84</v>
+        <v>5.15</v>
       </c>
       <c r="O25" t="n">
         <v>-0.96</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>6.17</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>218.6</v>
+        <v>214.6</v>
       </c>
       <c r="I26" t="n">
         <v>214.9987948924457</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.21</v>
+        <v>-4</v>
       </c>
       <c r="L26" t="n">
         <v>4.65</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="N26" t="n">
         <v>2.63</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>5.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45169.55208333334</v>
+        <v>45170.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>214.4</v>
+        <v>219.8</v>
       </c>
       <c r="I27" t="n">
         <v>217.8536242245814</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K27" t="n">
-        <v>0.09</v>
+        <v>-2.42</v>
       </c>
       <c r="L27" t="n">
         <v>2.73</v>
@@ -1980,7 +2303,7 @@
         <v>1.21</v>
       </c>
       <c r="N27" t="n">
-        <v>1.86</v>
+        <v>2.85</v>
       </c>
       <c r="O27" t="n">
         <v>-1.72</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.76</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>360.25</v>
+        <v>353.55</v>
       </c>
       <c r="I28" t="n">
         <v>355.1820764624626</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>144</v>
+        <v>144.1666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>63.9</v>
+        <v>60.85</v>
       </c>
       <c r="L28" t="n">
         <v>2.3</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>194</v>
+        <v>195</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>7.51</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>366.6</v>
+        <v>381.75</v>
       </c>
       <c r="I29" t="n">
         <v>380.1150180654053</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.69</v>
+        <v>-7.98</v>
       </c>
       <c r="L29" t="n">
-        <v>4.04</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>0.88</v>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>6.01</v>
       </c>
       <c r="O29" t="n">
         <v>-5.63</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>8.24</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45341.55208333334</v>
+        <v>45342.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>431.55</v>
+        <v>419.75</v>
       </c>
       <c r="I30" t="n">
         <v>420.0591868832826</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>13.05</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>3.69</v>
       </c>
       <c r="M30" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="N30" t="n">
         <v>4.29</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45386.38541666666</v>
+        <v>45386.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>419.1</v>
+        <v>422.15</v>
       </c>
       <c r="I31" t="n">
         <v>421.3442533742258</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K31" t="n">
-        <v>0.15</v>
+        <v>-0.57</v>
       </c>
       <c r="L31" t="n">
         <v>4.11</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>5</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45400.55208333334</v>
+        <v>45401.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>415.05</v>
+        <v>408.45</v>
       </c>
       <c r="I32" t="n">
         <v>409.5286617649813</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.68</v>
+        <v>-3.25</v>
       </c>
       <c r="L32" t="n">
-        <v>3.2</v>
+        <v>4.79</v>
       </c>
       <c r="M32" t="n">
         <v>1.54</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>5.6</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45414.55208333334</v>
+        <v>45415.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>424.45</v>
+        <v>436.55</v>
       </c>
       <c r="I33" t="n">
         <v>431.3324938382448</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.92</v>
+        <v>-6.88</v>
       </c>
       <c r="L33" t="n">
-        <v>5.86</v>
+        <v>8.69</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="N33" t="n">
-        <v>1.97</v>
+        <v>5.17</v>
       </c>
       <c r="O33" t="n">
         <v>-1.42</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>6.35</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>481.25</v>
+        <v>420.1</v>
       </c>
       <c r="I34" t="n">
         <v>453.7705554917139</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K34" t="n">
-        <v>10.24</v>
+        <v>-3.77</v>
       </c>
       <c r="L34" t="n">
-        <v>6.49</v>
+        <v>11.64</v>
       </c>
       <c r="M34" t="n">
         <v>0.9</v>
       </c>
       <c r="N34" t="n">
-        <v>4.62</v>
+        <v>13.56</v>
       </c>
       <c r="O34" t="n">
         <v>5.17</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>16.37</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45476.55208333334</v>
+        <v>45477.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>454.95</v>
+        <v>459.45</v>
       </c>
       <c r="I35" t="n">
         <v>458.7800336087779</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K35" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L35" t="n">
         <v>14.53</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>4.25</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45492.38541666666</v>
+        <v>45492.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>459.75</v>
+        <v>458.25</v>
       </c>
       <c r="I36" t="n">
         <v>459.2305276062152</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="L36" t="n">
         <v>1.78</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>5.91</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45502.55208333334</v>
+        <v>45503.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>480.4</v>
+        <v>488.3</v>
       </c>
       <c r="I37" t="n">
         <v>482.2960201105829</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.83</v>
+        <v>-6.56</v>
       </c>
       <c r="L37" t="n">
-        <v>5.68</v>
+        <v>7.71</v>
       </c>
       <c r="M37" t="n">
         <v>1.18</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>6.54</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>492.65</v>
+        <v>474.05</v>
       </c>
       <c r="I38" t="n">
         <v>476.6762843050386</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K38" t="n">
-        <v>0.89</v>
+        <v>-2.92</v>
       </c>
       <c r="L38" t="n">
-        <v>1.94</v>
+        <v>4.32</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="N38" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="O38" t="n">
         <v>1.45</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>7.5</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45526.55208333334</v>
+        <v>45527.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>497.15</v>
+        <v>506.55</v>
       </c>
       <c r="I39" t="n">
         <v>502.7861642071134</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.87</v>
+        <v>-6.86</v>
       </c>
       <c r="L39" t="n">
-        <v>6.08</v>
+        <v>7.1</v>
       </c>
       <c r="M39" t="n">
         <v>1.47</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.4</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>487.15</v>
+        <v>473.6</v>
       </c>
       <c r="I40" t="n">
         <v>485.6781285969868</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.83</v>
+        <v>-6.5</v>
       </c>
       <c r="L40" t="n">
-        <v>4.33</v>
+        <v>7.22</v>
       </c>
       <c r="M40" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="N40" t="n">
-        <v>1.22</v>
+        <v>2.66</v>
       </c>
       <c r="O40" t="n">
         <v>1.59</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.92</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45558.38541666666</v>
+        <v>45558.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>467.35</v>
+        <v>470.95</v>
       </c>
       <c r="I41" t="n">
         <v>469.4622704607768</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>1.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L41" t="n">
         <v>2.48</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.91</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>468.1</v>
+        <v>449.95</v>
       </c>
       <c r="I42" t="n">
         <v>464.074991650808</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.61</v>
+        <v>-4.46</v>
       </c>
       <c r="L42" t="n">
-        <v>1.49</v>
+        <v>4.84</v>
       </c>
       <c r="M42" t="n">
         <v>1.77</v>
       </c>
       <c r="N42" t="n">
-        <v>1.28</v>
+        <v>3.43</v>
       </c>
       <c r="O42" t="n">
         <v>2.04</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.62</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>382.4</v>
+        <v>387</v>
       </c>
       <c r="I43" t="n">
         <v>382.5863098641269</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>87.16666666666667</v>
+        <v>88</v>
       </c>
       <c r="K43" t="n">
-        <v>15.01</v>
+        <v>13.99</v>
       </c>
       <c r="L43" t="n">
         <v>4.86</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>4.98</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>371.2</v>
+        <v>369.5</v>
       </c>
       <c r="I44" t="n">
         <v>369.9222998438438</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.08</v>
+        <v>-4.52</v>
       </c>
       <c r="L44" t="n">
-        <v>4.16</v>
+        <v>5.12</v>
       </c>
       <c r="M44" t="n">
         <v>0.01</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>4.64</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>370.95</v>
+        <v>376.45</v>
       </c>
       <c r="I45" t="n">
         <v>372.52601939748</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.39</v>
+        <v>-1.88</v>
       </c>
       <c r="L45" t="n">
-        <v>1.24</v>
+        <v>2.03</v>
       </c>
       <c r="M45" t="n">
         <v>1.18</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>6.02</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45695.55208333334</v>
+        <v>45698.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>368.75</v>
+        <v>360.2</v>
       </c>
       <c r="I46" t="n">
         <v>361.3944631910787</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.05</v>
+        <v>-4.32</v>
       </c>
       <c r="L46" t="n">
         <v>5.21</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>7.19</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>358.55</v>
+        <v>372.95</v>
       </c>
       <c r="I47" t="n">
         <v>365.6646065918346</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>0.46</v>
+        <v>-3.54</v>
       </c>
       <c r="L47" t="n">
-        <v>2.68</v>
+        <v>3.83</v>
       </c>
       <c r="M47" t="n">
         <v>1.05</v>
       </c>
       <c r="N47" t="n">
-        <v>2.02</v>
+        <v>3.77</v>
       </c>
       <c r="O47" t="n">
         <v>-2.07</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>386.4</v>
+        <v>374.5</v>
       </c>
       <c r="I48" t="n">
         <v>378.8292882008611</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K48" t="n">
-        <v>3.61</v>
+        <v>0.42</v>
       </c>
       <c r="L48" t="n">
         <v>3.93</v>
@@ -3177,7 +3752,7 @@
         <v>0.97</v>
       </c>
       <c r="N48" t="n">
-        <v>2.11</v>
+        <v>2.86</v>
       </c>
       <c r="O48" t="n">
         <v>3.77</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.45</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>365.35</v>
+        <v>381.75</v>
       </c>
       <c r="I49" t="n">
         <v>381.0027220272419</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K49" t="n">
-        <v>2.44</v>
+        <v>-1.94</v>
       </c>
       <c r="L49" t="n">
         <v>2.95</v>
       </c>
       <c r="M49" t="n">
-        <v>1.85</v>
+        <v>3.91</v>
       </c>
       <c r="N49" t="n">
-        <v>1.24</v>
+        <v>4.42</v>
       </c>
       <c r="O49" t="n">
         <v>-2.86</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>7.88</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45782.55208333334</v>
+        <v>45783.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>375.75</v>
+        <v>370.8</v>
       </c>
       <c r="I50" t="n">
         <v>372.4673259868789</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.57</v>
+        <v>-2.87</v>
       </c>
       <c r="L50" t="n">
-        <v>2.72</v>
+        <v>3.43</v>
       </c>
       <c r="M50" t="n">
         <v>0.72</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.28</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>384.95</v>
+        <v>387.05</v>
       </c>
       <c r="I51" t="n">
         <v>385.8120837705588</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.82</v>
+        <v>-4.38</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>4.92</v>
       </c>
       <c r="M51" t="n">
         <v>2.29</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>4.87</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45810.55208333334</v>
+        <v>45811.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>388.65</v>
+        <v>381.35</v>
       </c>
       <c r="I52" t="n">
         <v>382.2262064670976</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
-        <v>0.41</v>
+        <v>-1.47</v>
       </c>
       <c r="L52" t="n">
-        <v>1.09</v>
+        <v>1.77</v>
       </c>
       <c r="M52" t="n">
         <v>0.1</v>
       </c>
       <c r="N52" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="O52" t="n">
         <v>0.13</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.71</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45861.38541666666</v>
+        <v>45861.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>379.95</v>
+        <v>380.5</v>
       </c>
       <c r="I53" t="n">
         <v>380.1303516520583</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K53" t="n">
-        <v>0.37</v>
+        <v>0.22</v>
       </c>
       <c r="L53" t="n">
         <v>4.55</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>2.55</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45863.55208333334</v>
+        <v>45866.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>371.55</v>
+        <v>368.85</v>
       </c>
       <c r="I54" t="n">
         <v>370.7828830773539</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.35</v>
+        <v>-3.06</v>
       </c>
       <c r="L54" t="n">
-        <v>2.76</v>
+        <v>3.07</v>
       </c>
       <c r="M54" t="n">
         <v>0.18</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>3.45</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45881.55208333334</v>
+        <v>45882.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>375.1</v>
+        <v>377</v>
       </c>
       <c r="I55" t="n">
         <v>376.5739010025777</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K55" t="n">
-        <v>-1.69</v>
+        <v>-2.21</v>
       </c>
       <c r="L55" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="M55" t="n">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="N55" t="n">
         <v>1.58</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>3.29</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45890.38541666666</v>
+        <v>45890.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>370</v>
+        <v>367.3</v>
       </c>
       <c r="I56" t="n">
         <v>367.4447022801753</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.86</v>
+        <v>-2.57</v>
       </c>
       <c r="L56" t="n">
-        <v>2.19</v>
+        <v>2.57</v>
       </c>
       <c r="M56" t="n">
         <v>1.07</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>3.13</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45902.55208333334</v>
+        <v>45903.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>369.95</v>
+        <v>380.95</v>
       </c>
       <c r="I57" t="n">
         <v>374.6116412844686</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.72</v>
+        <v>-3.72</v>
       </c>
       <c r="L57" t="n">
-        <v>2.06</v>
+        <v>4.25</v>
       </c>
       <c r="M57" t="n">
         <v>0.8</v>
       </c>
       <c r="N57" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="O57" t="n">
         <v>-2.03</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.1</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45926.55208333334</v>
+        <v>45929.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>378.85</v>
+        <v>376.1</v>
       </c>
       <c r="I58" t="n">
         <v>378.736656782199</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.55</v>
+        <v>-1.27</v>
       </c>
       <c r="L58" t="n">
         <v>2.87</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>3.53</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>380.65</v>
+        <v>383.25</v>
       </c>
       <c r="I59" t="n">
         <v>380.6685429915767</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>22.1875</v>
+        <v>24</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.21</v>
+        <v>-1.9</v>
       </c>
       <c r="L59" t="n">
         <v>2.23</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>2.7</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45959.38541666666</v>
+        <v>45959.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>386.2</v>
+        <v>372.85</v>
       </c>
       <c r="I60" t="n">
         <v>377.2905452613735</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>0.77</v>
+        <v>-2.71</v>
       </c>
       <c r="L60" t="n">
-        <v>1.08</v>
+        <v>3.46</v>
       </c>
       <c r="M60" t="n">
         <v>0.03</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>5.87</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>382.9</v>
+        <v>386.8</v>
       </c>
       <c r="I61" t="n">
         <v>386.4687455170707</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.7</v>
+        <v>-3.74</v>
       </c>
       <c r="L61" t="n">
         <v>3.97</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>3.5</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45982.55208333334</v>
+        <v>45985.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>378.45</v>
+        <v>373.25</v>
       </c>
       <c r="I62" t="n">
         <v>377.3008517425043</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.16</v>
+        <v>-3.5</v>
       </c>
       <c r="L62" t="n">
-        <v>2.39</v>
+        <v>3.57</v>
       </c>
       <c r="M62" t="n">
         <v>0.53</v>
       </c>
       <c r="N62" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="O62" t="n">
         <v>0.86</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>3.38</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45995.55208333334</v>
+        <v>45996.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>378.8</v>
+        <v>380</v>
       </c>
       <c r="I63" t="n">
         <v>379.8511527105566</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.49</v>
+        <v>-1.81</v>
       </c>
       <c r="L63" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="M63" t="n">
         <v>0.5</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>3.06</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>440</v>
+        <v>427.75</v>
       </c>
       <c r="I64" t="n">
         <v>429.7627838523437</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K64" t="n">
-        <v>15.79</v>
+        <v>12.57</v>
       </c>
       <c r="L64" t="n">
         <v>1.75</v>
@@ -4089,7 +4856,7 @@
         <v>0.5</v>
       </c>
       <c r="N64" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="O64" t="n">
         <v>0.16</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>7.85</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46077.38541666666</v>
+        <v>46077.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>426.4</v>
+        <v>431.45</v>
       </c>
       <c r="I65" t="n">
         <v>429.0634052648502</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>0.32</v>
+        <v>-0.86</v>
       </c>
       <c r="L65" t="n">
         <v>3.19</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>5.18</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46121.55208333334</v>
+        <v>46122.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>454.4</v>
+        <v>438.35</v>
       </c>
       <c r="I66" t="n">
         <v>440.7576664820382</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>44</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>5.32</v>
+        <v>1.6</v>
       </c>
       <c r="L66" t="n">
         <v>3.58</v>
@@ -4203,7 +4994,7 @@
         <v>3.01</v>
       </c>
       <c r="N66" t="n">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="O66" t="n">
         <v>1.28</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>8.85</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>450.9</v>
+        <v>455.45</v>
       </c>
       <c r="I67" t="n">
         <v>454.0590868148054</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.86</v>
+        <v>-3.9</v>
       </c>
       <c r="L67" t="n">
-        <v>4.85</v>
+        <v>5.4</v>
       </c>
       <c r="M67" t="n">
         <v>0.8</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>3.7</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46149.55208333334</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>465.5</v>
+        <v>456.85</v>
       </c>
       <c r="I68" t="n">
         <v>459.128281211893</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>2.21</v>
+        <v>0.31</v>
       </c>
       <c r="L68" t="n">
         <v>1.05</v>
       </c>
       <c r="M68" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N68" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="O68" t="n">
         <v>0.91</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>6.23</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>458.3</v>
+        <v>471</v>
       </c>
       <c r="I69" t="n">
         <v>470.235511233767</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.32</v>
+        <v>-3.1</v>
       </c>
       <c r="L69" t="n">
-        <v>4.12</v>
+        <v>4.41</v>
       </c>
       <c r="M69" t="n">
         <v>0.88</v>
       </c>
       <c r="N69" t="n">
-        <v>1.69</v>
+        <v>3.31</v>
       </c>
       <c r="O69" t="n">
         <v>-1.92</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46183.38541666666</v>
+        <v>46183.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>459.5</v>
+        <v>451.35</v>
       </c>
       <c r="I70" t="n">
         <v>453.4586561932294</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.44</v>
+        <v>-4.17</v>
       </c>
       <c r="L70" t="n">
-        <v>3.07</v>
+        <v>4.42</v>
       </c>
       <c r="M70" t="n">
         <v>1.42</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>6.43</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>402.4</v>
+        <v>415.9</v>
       </c>
       <c r="I71" t="n">
         <v>409.8666834014543</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>83</v>
+        <v>83.83333333333333</v>
       </c>
       <c r="K71" t="n">
-        <v>10.85</v>
+        <v>7.85</v>
       </c>
       <c r="L71" t="n">
         <v>2.26</v>
@@ -4488,7 +5339,7 @@
         <v>1.65</v>
       </c>
       <c r="N71" t="n">
-        <v>1.88</v>
+        <v>3.48</v>
       </c>
       <c r="O71" t="n">
         <v>-3.17</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>4</v>
+      </c>
+      <c r="U71" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>4.5</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>417.45</v>
+        <v>411.35</v>
       </c>
       <c r="I72" t="n">
         <v>417.0355368329702</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K72" t="n">
-        <v>0.37</v>
+        <v>-1.09</v>
       </c>
       <c r="L72" t="n">
         <v>2.26</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>4.82</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46294.55208333334</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>424.1</v>
+        <v>429.75</v>
       </c>
       <c r="I73" t="n">
         <v>427.7858461993564</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K73" t="n">
-        <v>-3.1</v>
+        <v>-4.47</v>
       </c>
       <c r="L73" t="n">
-        <v>4.39</v>
+        <v>5.24</v>
       </c>
       <c r="M73" t="n">
         <v>2.68</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>3.69</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46301.38541666666</v>
+        <v>46301.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>413.9</v>
+        <v>411.1</v>
       </c>
       <c r="I74" t="n">
         <v>413.898547428216</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.69</v>
+        <v>-4.34</v>
       </c>
       <c r="L74" t="n">
-        <v>3.92</v>
+        <v>4.46</v>
       </c>
       <c r="M74" t="n">
         <v>0.65</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4719,6 +5618,14 @@
       <c r="Q75" t="n">
         <v>31</v>
       </c>
+      <c r="R75" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6821,7 +7728,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.6</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="6">
@@ -6831,7 +7738,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -6841,7 +7748,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="8">
@@ -6851,7 +7758,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6861,7 +7768,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -6871,7 +7778,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44.9</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="11">
@@ -6911,7 +7818,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.72</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="15">
@@ -6921,7 +7828,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="16">
@@ -6931,7 +7838,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.31</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="17">
@@ -6941,7 +7848,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63.9</v>
+        <v>60.85</v>
       </c>
     </row>
     <row r="18">
@@ -6951,7 +7858,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.2</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="19">
@@ -6961,7 +7868,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.4</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="20">
@@ -6971,7 +7878,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.06</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="21">
@@ -6991,7 +7898,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -7001,7 +7908,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -7011,7 +7918,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="25">
@@ -7021,7 +7928,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.56</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="26">
@@ -7031,7 +7938,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="27">
@@ -7041,7 +7948,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.140000000000001</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="28">
@@ -7051,7 +7958,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
